--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
 </t>
   </si>
   <si>
@@ -2308,10 +2308,10 @@
     <t>Composition.event.extension</t>
   </si>
   <si>
-    <t>Composition.event.extension:perfomer</t>
-  </si>
-  <si>
-    <t>perfomer</t>
+    <t>Composition.event.extension:performer</t>
+  </si>
+  <si>
+    <t>performer</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-performer-event}
@@ -2391,7 +2391,7 @@
     <t>Composition.event:principalEvent.extension</t>
   </si>
   <si>
-    <t>Composition.event:principalEvent.extension:perfomer</t>
+    <t>Composition.event:principalEvent.extension:performer</t>
   </si>
   <si>
     <t>Exécutant de l'évènement documenté principal</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2321,7 +2321,7 @@
     <t>Exécutant de l’évènement documenté</t>
   </si>
   <si>
-    <t>Extension permettant d'ajouter un perfomer à l'élément event d'une Composition.</t>
+    <t>Extension permettant d'ajouter un performer à l'élément event d'une Composition.</t>
   </si>
   <si>
     <t>Composition.event.modifierExtension</t>
